--- a/src/nodes/HPC/compressor_stage_9_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_9_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-13.868464822932673</v>
+        <v>-13.861256511726804</v>
       </c>
       <c r="B1">
-        <v>4.8439900312958963</v>
+        <v>4.8645784898926347</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-12.816983220165518</v>
+        <v>-12.826972398950192</v>
       </c>
       <c r="B2">
-        <v>5.2886523356968791</v>
+        <v>5.2630209977834577</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-11.932927390188223</v>
+        <v>-11.949638267227964</v>
       </c>
       <c r="B3">
-        <v>5.3127865136059658</v>
+        <v>5.2689447895486277</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-11.073491960192198</v>
+        <v>-11.095471979641946</v>
       </c>
       <c r="B4">
-        <v>5.2750809251213813</v>
+        <v>5.2169277496255679</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-10.23074133115907</v>
+        <v>-10.257039220721559</v>
       </c>
       <c r="B5">
-        <v>5.1954676424216268</v>
+        <v>5.12556247639612</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-9.4014414125381016</v>
+        <v>-9.4313101190045554</v>
       </c>
       <c r="B6">
-        <v>5.082069823713125</v>
+        <v>5.00242642382619</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-8.58374708394275</v>
+        <v>-8.6165560190106181</v>
       </c>
       <c r="B7">
-        <v>4.9395219109122932</v>
+        <v>4.8518428140353276</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-7.7765743161050436</v>
+        <v>-7.8117612707035669</v>
       </c>
       <c r="B8">
-        <v>4.7705466914939931</v>
+        <v>4.6763517024319867</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-6.9782270550060925</v>
+        <v>-7.0153368822533713</v>
       </c>
       <c r="B9">
-        <v>4.5794041930938123</v>
+        <v>4.4799270240804994</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.1868738999067272</v>
+        <v>-6.2255670726814891</v>
       </c>
       <c r="B10">
-        <v>4.3706943975954582</v>
+        <v>4.2668598030531495</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.4007540879375862</v>
+        <v>-5.4408022462092047</v>
       </c>
       <c r="B11">
-        <v>4.14883986371441</v>
+        <v>4.0412755397981659</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.6189283529172744</v>
+        <v>-4.66016240146682</v>
       </c>
       <c r="B12">
-        <v>3.9161997733194904</v>
+        <v>3.8053750438059435</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-3.8436727775464217</v>
+        <v>-3.8857797295209004</v>
       </c>
       <c r="B13">
-        <v>3.6670572240611623</v>
+        <v>3.5538258843596373</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-3.0763490911567763</v>
+        <v>-3.1189298483870953</v>
       </c>
       <c r="B14">
-        <v>3.3979919212313416</v>
+        <v>3.2834378479759092</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.3114462607225459</v>
+        <v>-2.3544498914411283</v>
       </c>
       <c r="B15">
-        <v>3.1228460849061466</v>
+        <v>3.0071228303126927</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.5439095933534126</v>
+        <v>-1.5876045023785308</v>
       </c>
       <c r="B16">
-        <v>2.8543157325250594</v>
+        <v>2.7367235596362907</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-0.77738251905847378</v>
+        <v>-0.821806850813976</v>
       </c>
       <c r="B17">
-        <v>2.5832495561968178</v>
+        <v>2.4637039855052061</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.016569622720318693</v>
+        <v>-0.061464216753222362</v>
       </c>
       <c r="B18">
-        <v>2.2978309148294964</v>
+        <v>2.177041870912181</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.73827801418395189</v>
+        <v>0.69318820415280269</v>
       </c>
       <c r="B19">
-        <v>1.9974291598592397</v>
+        <v>1.8761490112947195</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.4880226860286079</v>
+        <v>1.44295823734188</v>
       </c>
       <c r="B20">
-        <v>1.6842101408542118</v>
+        <v>1.563045710201511</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.233526687187918</v>
+        <v>2.188653708251787</v>
       </c>
       <c r="B21">
-        <v>1.3603397073825774</v>
+        <v>1.2397522711812465</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2.9754988351975151</v>
+        <v>2.930938657761776</v>
       </c>
       <c r="B22">
-        <v>1.0275982168248909</v>
+        <v>0.90792940468209238</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>3.7140340402384457</v>
+        <v>3.6699019885169486</v>
       </c>
       <c r="B23">
-        <v>0.686224057811285</v>
+        <v>0.56779944875011967</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4.449073735653128</v>
+        <v>4.4054888186038861</v>
       </c>
       <c r="B24">
-        <v>0.336070126784279</v>
+        <v>0.21922514833087164</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.1805593547839655</v>
+        <v>5.1376442661091559</v>
       </c>
       <c r="B25">
-        <v>-0.023010679813602719</v>
+        <v>-0.13793075163010438</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>5.90840705531128</v>
+        <v>5.866289765337303</v>
       </c>
       <c r="B26">
-        <v>-0.39122895114691292</v>
+        <v>-0.50386473733628523</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>6.6324318922670269</v>
+        <v>6.5912520154647369</v>
       </c>
       <c r="B27">
-        <v>-0.76904921880850552</v>
+        <v>-0.87901021958723791</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>7.3524236450210534</v>
+        <v>7.3123340318858236</v>
       </c>
       <c r="B28">
-        <v>-1.156999499998302</v>
+        <v>-1.2638598403315444</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>8.0681720929432252</v>
+        <v>8.0293388299949449</v>
       </c>
       <c r="B29">
-        <v>-1.5556078119162309</v>
+        <v>-1.6589062415177951</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>8.7795813866040753</v>
+        <v>8.7421765643964413</v>
       </c>
       <c r="B30">
-        <v>-1.9651149023296377</v>
+        <v>-2.0643741189319496</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>9.4870131613768844</v>
+        <v>9.4511859465345864</v>
       </c>
       <c r="B31">
-        <v>-2.3846124412755625</v>
+        <v>-2.4794163837094771</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>10.190943423835616</v>
+        <v>10.156812827063618</v>
       </c>
       <c r="B32">
-        <v>-2.8129048293584695</v>
+        <v>-2.9029180008232278</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>10.891848180554222</v>
+        <v>10.859503056637776</v>
       </c>
       <c r="B33">
-        <v>-3.2487964671828182</v>
+        <v>-3.3337639352460422</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>11.590018676406036</v>
+        <v>11.559529393168988</v>
       </c>
       <c r="B34">
-        <v>-3.6915558266278783</v>
+        <v>-3.7712720423565549</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>12.285007109461853</v>
+        <v>12.256472223599882</v>
       </c>
       <c r="B35">
-        <v>-4.14230766467214</v>
+        <v>-4.216491739156524</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>12.976180916091854</v>
+        <v>12.949738842130788</v>
       </c>
       <c r="B36">
-        <v>-4.6026408095689</v>
+        <v>-4.6709053330534989</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>13.66290753266621</v>
+        <v>13.63873654296202</v>
       </c>
       <c r="B37">
-        <v>-5.0741440895714591</v>
+        <v>-5.1359951314550285</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>14.344101254677755</v>
+        <v>14.322448106862225</v>
       </c>
       <c r="B38">
-        <v>-5.5595444999011017</v>
+        <v>-5.6143051141948446</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>15.016863814110034</v>
+        <v>14.998158260873391</v>
       </c>
       <c r="B39">
-        <v>-6.0661217036510768</v>
+        <v>-6.1126259508114407</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>15.677843802069244</v>
+        <v>15.662727218605825</v>
       </c>
       <c r="B40">
-        <v>-6.6022935308826156</v>
+        <v>-6.6388099832694945</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>16.323689809661587</v>
+        <v>16.313015193669834</v>
       </c>
       <c r="B41">
-        <v>-7.176477811656949</v>
+        <v>-7.2007095535336791</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>16.323689809661587</v>
+        <v>16.313015193669834</v>
       </c>
       <c r="B42">
-        <v>-7.176477811656949</v>
+        <v>-7.2007095535336791</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>15.519574719503256</v>
+        <v>15.514458619176573</v>
       </c>
       <c r="B43">
-        <v>-6.999822535312556</v>
+        <v>-7.0096172933356993</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>14.727507112194473</v>
+        <v>14.727085021344124</v>
       </c>
       <c r="B44">
-        <v>-6.7929072499668841</v>
+        <v>-6.7905573480709265</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>13.944139810617013</v>
+        <v>13.947758861337208</v>
       </c>
       <c r="B45">
-        <v>-6.5641391566088361</v>
+        <v>-6.5513714369273481</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13.166125637652653</v>
+        <v>13.173344600320545</v>
       </c>
       <c r="B46">
-        <v>-6.3219254562273148</v>
+        <v>-6.2999012790929516</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>12.390570408222756</v>
+        <v>12.401131063497825</v>
       </c>
       <c r="B47">
-        <v>-6.0735355566832148</v>
+        <v>-6.0429272949480906</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>11.616391905407124</v>
+        <v>11.630104532228669</v>
       </c>
       <c r="B48">
-        <v>-5.8216876933254218</v>
+        <v>-5.7829847096426015</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>10.842960904325155</v>
+        <v>10.859675651911676</v>
       </c>
       <c r="B49">
-        <v>-5.5679623083748124</v>
+        <v>-5.5215474495186916</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>10.069648180096246</v>
+        <v>10.089255067945439</v>
       </c>
       <c r="B50">
-        <v>-5.3139398440522649</v>
+        <v>-5.2600894409185637</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>9.2960091050655347</v>
+        <v>9.3184263533827139</v>
       </c>
       <c r="B51">
-        <v>-5.0607370844201984</v>
+        <v>-4.9996521326503</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>8.5223374404810528</v>
+        <v>8.5474647918928159</v>
       </c>
       <c r="B52">
-        <v>-4.80761618090718</v>
+        <v>-4.7395470633854551</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>7.7491115448165688</v>
+        <v>7.7768185947992308</v>
       </c>
       <c r="B53">
-        <v>-4.55337562678332</v>
+        <v>-4.47865329426146</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>6.976809776545851</v>
+        <v>7.006935973425434</v>
       </c>
       <c r="B54">
-        <v>-4.2968139153187277</v>
+        <v>-4.2158498864157421</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.2057959655818218</v>
+        <v>6.2381578419380226</v>
       </c>
       <c r="B55">
-        <v>-4.037017204462102</v>
+        <v>-3.9502842421602633</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5.43597582759408</v>
+        <v>5.47039592587612</v>
       </c>
       <c r="B56">
-        <v>-3.7742223108765258</v>
+        <v>-3.6821771285051295</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4.6671405496913687</v>
+        <v>4.7034546536219635</v>
       </c>
       <c r="B57">
-        <v>-3.5089537159036697</v>
+        <v>-3.4120176536349729</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3.8990813189824496</v>
+        <v>3.9371384535578029</v>
       </c>
       <c r="B58">
-        <v>-3.2417359008852102</v>
+        <v>-3.1402949257344335</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.1316144427351742</v>
+        <v>3.1712752817651086</v>
       </c>
       <c r="B59">
-        <v>-2.9730302521370704</v>
+        <v>-2.8674392121891077</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.3646567088538131</v>
+        <v>2.4057872051222606</v>
       </c>
       <c r="B60">
-        <v>-2.7030457758721775</v>
+        <v>-2.5936454171884336</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.598150025401752</v>
+        <v>1.6406198182068794</v>
       </c>
       <c r="B61">
-        <v>-2.4319283832777123</v>
+        <v>-2.319049604122815</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.83203630044236021</v>
+        <v>0.87571871559657066</v>
       </c>
       <c r="B62">
-        <v>-2.1598239855408514</v>
+        <v>-2.0437878363826507</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.066410757554462019</v>
+        <v>0.11117311450276546</v>
       </c>
       <c r="B63">
-        <v>-1.8864934068612984</v>
+        <v>-1.7676369892179478</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.69801811762137511</v>
+        <v>-0.65235327732787263</v>
       </c>
       <c r="B64">
-        <v>-1.6101571234888441</v>
+        <v>-1.4889371853171252</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.4603885239291381</v>
+        <v>-1.4140531295148622</v>
       </c>
       <c r="B65">
-        <v>-1.3286505246858036</v>
+        <v>-1.2056693592282071</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2198386602128148</v>
+        <v>-2.1731191116777229</v>
       </c>
       <c r="B66">
-        <v>-1.0398089997144921</v>
+        <v>-0.91581444549921731</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-2.9766202309646754</v>
+        <v>-2.9297870448055603</v>
       </c>
       <c r="B67">
-        <v>-0.74426476198387259</v>
+        <v>-0.61996221261089934</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-3.7354389632701124</v>
+        <v>-3.6884653553658193</v>
       </c>
       <c r="B68">
-        <v>-0.45383732148949918</v>
+        <v>-0.32913776477487405</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-4.4999396168082395</v>
+        <v>-4.4525685476010723</v>
       </c>
       <c r="B69">
-        <v>-0.17768132589301533</v>
+        <v>-0.051880490224862248</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.26506905903991</v>
+        <v>-5.217362831376037</v>
       </c>
       <c r="B70">
-        <v>0.096895323066157</v>
+        <v>0.22364842244787866</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.025317959558655</v>
+        <v>-5.9776870490342446</v>
       </c>
       <c r="B71">
-        <v>0.38373056894623225</v>
+        <v>0.51035659491637719</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-6.782050088706983</v>
+        <v>-6.7348188672123293</v>
       </c>
       <c r="B72">
-        <v>0.679398990573739</v>
+        <v>0.80504869026833037</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-7.5375437330702866</v>
+        <v>-7.4908926890791516</v>
       </c>
       <c r="B73">
-        <v>0.97817815003841524</v>
+        <v>1.1023867455049055</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-8.2908621434565433</v>
+        <v>-8.2450310396393824</v>
       </c>
       <c r="B74">
-        <v>1.2824209072145187</v>
+        <v>1.4045652518664735</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-9.040247232183221</v>
+        <v>-8.9955870082759741</v>
       </c>
       <c r="B75">
-        <v>1.596543101473878</v>
+        <v>1.7157029944375006</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-9.78387059338316</v>
+        <v>-9.7408478200492539</v>
       </c>
       <c r="B76">
-        <v>1.9251371923940832</v>
+        <v>2.0400834794396472</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-10.520039331533456</v>
+        <v>-10.479227653402131</v>
       </c>
       <c r="B77">
-        <v>2.2724552743255408</v>
+        <v>2.3816727133509787</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-11.247672910672881</v>
+        <v>-11.209714364630502</v>
       </c>
       <c r="B78">
-        <v>2.6412113605041534</v>
+        <v>2.743001982538003</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-11.964929855425581</v>
+        <v>-11.930582956855742</v>
       </c>
       <c r="B79">
-        <v>3.0360307375681916</v>
+        <v>3.1283853592648341</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-12.668580022176936</v>
+        <v>-12.638807520268474</v>
       </c>
       <c r="B80">
-        <v>3.4650266500911981</v>
+        <v>3.5453903897363723</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-13.350691992392624</v>
+        <v>-13.326957935469778</v>
       </c>
       <c r="B81">
-        <v>3.9481206700096938</v>
+        <v>4.01259917831182</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-13.868464822932673</v>
+        <v>-13.861256511726804</v>
       </c>
       <c r="B82">
-        <v>4.8439900312958963</v>
+        <v>4.8645784898926347</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-16.375799724065303</v>
+        <v>-16.376114470239049</v>
       </c>
       <c r="B1">
-        <v>4.5019847173697531</v>
+        <v>4.500839683409664</v>
       </c>
       <c r="C1">
         <v>214.35566444654796</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-15.359291560267611</v>
+        <v>-15.387428505945701</v>
       </c>
       <c r="B2">
-        <v>4.6160229035357725</v>
+        <v>4.5230949273698933</v>
       </c>
       <c r="C2">
         <v>214.35566444654796</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-14.406278912593105</v>
+        <v>-14.444933476980379</v>
       </c>
       <c r="B3">
-        <v>4.5204255976727161</v>
+        <v>4.3928086836344109</v>
       </c>
       <c r="C3">
         <v>214.35566444654796</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-13.462820023980187</v>
+        <v>-13.509584447104041</v>
       </c>
       <c r="B4">
-        <v>4.3932857970968291</v>
+        <v>4.2389234085226466</v>
       </c>
       <c r="C4">
         <v>214.35566444654796</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-12.525917743688622</v>
+        <v>-12.579211866822472</v>
       </c>
       <c r="B5">
-        <v>4.244498833139815</v>
+        <v>4.068603847782386</v>
       </c>
       <c r="C5">
         <v>214.35566444654796</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-11.594350809490397</v>
+        <v>-11.652931639291214</v>
       </c>
       <c r="B6">
-        <v>4.0780968000926814</v>
+        <v>3.8847696532232909</v>
       </c>
       <c r="C6">
         <v>214.35566444654796</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-10.667422589732903</v>
+        <v>-10.730239420551431</v>
       </c>
       <c r="B7">
-        <v>3.8963796827129853</v>
+        <v>3.6890863762623956</v>
       </c>
       <c r="C7">
         <v>214.35566444654796</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-9.7447239272717834</v>
+        <v>-9.810838954193331</v>
       </c>
       <c r="B8">
-        <v>3.7006983458257334</v>
+        <v>3.4825323775492532</v>
       </c>
       <c r="C8">
         <v>214.35566444654796</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-8.8256144528968132</v>
+        <v>-8.8942666338844845</v>
       </c>
       <c r="B9">
-        <v>3.4931670192641664</v>
+        <v>3.2666386760846922</v>
       </c>
       <c r="C9">
         <v>214.35566444654796</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-7.909402657645618</v>
+        <v>-7.9800218410572956</v>
       </c>
       <c r="B10">
-        <v>3.2760687748169923</v>
+        <v>3.0430585205099554</v>
       </c>
       <c r="C10">
         <v>214.35566444654796</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-6.9954236856130461</v>
+        <v>-7.0676232581261287</v>
       </c>
       <c r="B11">
-        <v>3.0515986870865537</v>
+        <v>2.813381419676642</v>
       </c>
       <c r="C11">
         <v>214.35566444654796</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-6.0833229721053579</v>
+        <v>-6.1568141707582384</v>
       </c>
       <c r="B12">
-        <v>2.8209273795840266</v>
+        <v>2.5784551500142832</v>
       </c>
       <c r="C12">
         <v>214.35566444654796</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-5.1739604642172337</v>
+        <v>-5.2482169766505278</v>
       </c>
       <c r="B13">
-        <v>2.5812156686422956</v>
+        <v>2.3362242980537844</v>
       </c>
       <c r="C13">
         <v>214.35566444654796</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-4.2678507137958217</v>
+        <v>-4.342204069496014</v>
       </c>
       <c r="B14">
-        <v>2.3307647204501403</v>
+        <v>2.0854590664866892</v>
       </c>
       <c r="C14">
         <v>214.35566444654796</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.3629121799097184</v>
+        <v>-3.4372687149425514</v>
       </c>
       <c r="B15">
-        <v>2.076446907798204</v>
+        <v>1.8311353125457175</v>
       </c>
       <c r="C15">
         <v>214.35566444654796</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.4572356830863251</v>
+        <v>-2.5320289434044421</v>
       </c>
       <c r="B16">
-        <v>1.8245655384245287</v>
+        <v>1.5778168688325729</v>
       </c>
       <c r="C16">
         <v>214.35566444654796</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.5521975824667957</v>
+        <v>-1.6274809724069037</v>
       </c>
       <c r="B17">
-        <v>1.57057645325488</v>
+        <v>1.32221381488372</v>
       </c>
       <c r="C17">
         <v>214.35566444654796</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.64957505253428127</v>
+        <v>-0.72491114792189648</v>
       </c>
       <c r="B18">
-        <v>1.3086121695133863</v>
+        <v>1.0600781066433005</v>
       </c>
       <c r="C18">
         <v>214.35566444654796</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.2505370094738</v>
+        <v>0.17561185740255411</v>
       </c>
       <c r="B19">
-        <v>1.0383593764299113</v>
+        <v>0.791182958751409</v>
       </c>
       <c r="C19">
         <v>214.35566444654796</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.1484642756314765</v>
+        <v>1.0743237892494184</v>
       </c>
       <c r="B20">
-        <v>0.760893306235748</v>
+        <v>0.51630690052212513</v>
       </c>
       <c r="C20">
         <v>214.35566444654796</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.0445324180127726</v>
+        <v>1.9714603933016637</v>
       </c>
       <c r="B21">
-        <v>0.47728919116219015</v>
+        <v>0.23622846126952951</v>
       </c>
       <c r="C21">
         <v>214.35566444654796</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2.9390091500031708</v>
+        <v>2.8672154584118692</v>
       </c>
       <c r="B22">
-        <v>0.1884309082247343</v>
+        <v>-0.048412388422080045</v>
       </c>
       <c r="C22">
         <v>214.35566444654796</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>3.8319303502339879</v>
+        <v>3.76161494611106</v>
       </c>
       <c r="B23">
-        <v>-0.10556308642431186</v>
+        <v>-0.33752991288753437</v>
       </c>
       <c r="C23">
         <v>214.35566444654796</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>4.72327393864799</v>
+        <v>4.6546428610998642</v>
       </c>
       <c r="B24">
-        <v>-0.40476569184843647</v>
+        <v>-0.631176935191445</v>
       </c>
       <c r="C24">
         <v>214.35566444654796</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>5.6130178351879527</v>
+        <v>5.5462832080789255</v>
       </c>
       <c r="B25">
-        <v>-0.70924980711113117</v>
+        <v>-0.929406278398426</v>
       </c>
       <c r="C25">
         <v>214.35566444654796</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>6.5011304263038872</v>
+        <v>6.4365130868342977</v>
       </c>
       <c r="B26">
-        <v>-1.0191198068597622</v>
+        <v>-1.2322935684441083</v>
       </c>
       <c r="C26">
         <v>214.35566444654796</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>7.3875419644748188</v>
+        <v>7.3252819774937876</v>
       </c>
       <c r="B27">
-        <v>-1.3346059680772271</v>
+        <v>-1.5400056427482136</v>
       </c>
       <c r="C27">
         <v>214.35566444654796</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>8.2721731686869955</v>
+        <v>8.2125324552706136</v>
       </c>
       <c r="B28">
-        <v>-1.6559700433302951</v>
+        <v>-1.8527321416014786</v>
       </c>
       <c r="C28">
         <v>214.35566444654796</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>9.1549447579266925</v>
+        <v>9.0982070953780081</v>
       </c>
       <c r="B29">
-        <v>-1.9834737851857422</v>
+        <v>-2.1706627052946437</v>
       </c>
       <c r="C29">
         <v>214.35566444654796</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>10.03582066702992</v>
+        <v>9.98227974979534</v>
       </c>
       <c r="B30">
-        <v>-2.3172362656482721</v>
+        <v>-2.4938836853583157</v>
       </c>
       <c r="C30">
         <v>214.35566444654796</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>10.91493769423178</v>
+        <v>10.864849377566607</v>
       </c>
       <c r="B31">
-        <v>-2.65680583447432</v>
+        <v>-2.8220682782825821</v>
       </c>
       <c r="C31">
         <v>214.35566444654796</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>11.792475853617127</v>
+        <v>11.746046214501956</v>
       </c>
       <c r="B32">
-        <v>-3.0015881608582577</v>
+        <v>-3.1547863917974004</v>
       </c>
       <c r="C32">
         <v>214.35566444654796</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>12.668615159270823</v>
+        <v>12.626000496411525</v>
       </c>
       <c r="B33">
-        <v>-3.3509889139944509</v>
+        <v>-3.4916079336327268</v>
       </c>
       <c r="C33">
         <v>214.35566444654796</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>13.543465849868479</v>
+        <v>13.504791948938124</v>
       </c>
       <c r="B34">
-        <v>-3.7046441321354795</v>
+        <v>-3.8322696168887806</v>
       </c>
       <c r="C34">
         <v>214.35566444654796</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>14.416859062448694</v>
+        <v>14.382298257055183</v>
       </c>
       <c r="B35">
-        <v>-4.0631113297667536</v>
+        <v>-4.17717537614682</v>
       </c>
       <c r="C35">
         <v>214.35566444654796</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>15.288556158640821</v>
+        <v>15.25834659556879</v>
       </c>
       <c r="B36">
-        <v>-4.4271783904318918</v>
+        <v>-4.5268959513583642</v>
       </c>
       <c r="C36">
         <v>214.35566444654796</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>16.158318500074227</v>
+        <v>16.132764139285051</v>
       </c>
       <c r="B37">
-        <v>-4.7976331976745215</v>
+        <v>-4.8820020824749362</v>
       </c>
       <c r="C37">
         <v>214.35566444654796</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>17.025736296317504</v>
+        <v>17.005254173561536</v>
       </c>
       <c r="B38">
-        <v>-5.1758287071670592</v>
+        <v>-5.243473643418854</v>
       </c>
       <c r="C38">
         <v>214.35566444654796</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>17.889715148696332</v>
+        <v>17.875024425961794</v>
       </c>
       <c r="B39">
-        <v>-5.5653781630971384</v>
+        <v>-5.613927043995635</v>
       </c>
       <c r="C39">
         <v>214.35566444654796</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>18.748989506475617</v>
+        <v>18.741158734600841</v>
       </c>
       <c r="B40">
-        <v>-5.970459881781192</v>
+        <v>-5.99638782798159</v>
       </c>
       <c r="C40">
         <v>214.35566444654796</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>19.602293818920252</v>
+        <v>19.602740937593715</v>
       </c>
       <c r="B41">
-        <v>-6.395252179535647</v>
+        <v>-6.39388153915303</v>
       </c>
       <c r="C41">
         <v>214.35566444654796</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>19.602293818920252</v>
+        <v>19.602740937593715</v>
       </c>
       <c r="B42">
-        <v>-6.395252179535647</v>
+        <v>-6.39388153915303</v>
       </c>
       <c r="C42">
         <v>214.35566444654796</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>18.689206209189457</v>
+        <v>18.697885619458468</v>
       </c>
       <c r="B43">
-        <v>-6.1678391883355248</v>
+        <v>-6.1392934720039216</v>
       </c>
       <c r="C43">
         <v>214.35566444654796</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>17.780415862620377</v>
+        <v>17.795910010965482</v>
       </c>
       <c r="B44">
-        <v>-5.9262384413332825</v>
+        <v>-5.8751954178878014</v>
       </c>
       <c r="C44">
         <v>214.35566444654796</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>16.874658059648542</v>
+        <v>16.89589878120854</v>
       </c>
       <c r="B45">
-        <v>-5.6746255106694949</v>
+        <v>-5.6046101763470135</v>
       </c>
       <c r="C45">
         <v>214.35566444654796</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>15.970668080709515</v>
+        <v>15.996936599281419</v>
       </c>
       <c r="B46">
-        <v>-5.4171759684847327</v>
+        <v>-5.3305605469239019</v>
       </c>
       <c r="C46">
         <v>214.35566444654796</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>15.067352329578132</v>
+        <v>15.098231995011604</v>
       </c>
       <c r="B47">
-        <v>-5.1575004096167838</v>
+        <v>-5.0556602900180367</v>
       </c>
       <c r="C47">
         <v>214.35566444654796</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>14.164301703386588</v>
+        <v>14.19948894116153</v>
       </c>
       <c r="B48">
-        <v>-4.8969495196923347</v>
+        <v>-4.78088700945793</v>
       </c>
       <c r="C48">
         <v>214.35566444654796</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>13.26127822260638</v>
+        <v>13.300535271227332</v>
       </c>
       <c r="B49">
-        <v>-4.636309007035285</v>
+        <v>-4.50680926992932</v>
       </c>
       <c r="C49">
         <v>214.35566444654796</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>12.358043907709018</v>
+        <v>12.401198818705167</v>
       </c>
       <c r="B50">
-        <v>-4.3763645799695388</v>
+        <v>-4.2339956361179478</v>
       </c>
       <c r="C50">
         <v>214.35566444654796</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>11.454430522443182</v>
+        <v>11.501357895133856</v>
       </c>
       <c r="B51">
-        <v>-4.1176716838474281</v>
+        <v>-3.9628479734281776</v>
       </c>
       <c r="C51">
         <v>214.35566444654796</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>10.550548803666196</v>
+        <v>10.601092724222919</v>
       </c>
       <c r="B52">
-        <v>-3.8598647121349794</v>
+        <v>-3.6931013501388481</v>
       </c>
       <c r="C52">
         <v>214.35566444654796</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9.646579231512554</v>
+        <v>9.700534007724551</v>
       </c>
       <c r="B53">
-        <v>-3.6023477953266472</v>
+        <v>-3.4243241352474159</v>
       </c>
       <c r="C53">
         <v>214.35566444654796</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>8.74270228611676</v>
+        <v>8.799812447390936</v>
       </c>
       <c r="B54">
-        <v>-3.344525063916886</v>
+        <v>-3.1560846977513428</v>
       </c>
       <c r="C54">
         <v>214.35566444654796</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>7.8390552006980734</v>
+        <v>7.8990274371498277</v>
       </c>
       <c r="B55">
-        <v>-3.0859434315273031</v>
+        <v>-2.8880547979754758</v>
       </c>
       <c r="C55">
         <v>214.35566444654796</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6.935602220814868</v>
+        <v>6.9981531396312127</v>
       </c>
       <c r="B56">
-        <v>-2.8267209442881316</v>
+        <v>-2.6203197615542244</v>
       </c>
       <c r="C56">
         <v>214.35566444654796</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6.0322643451102662</v>
+        <v>6.0971324096406248</v>
       </c>
       <c r="B57">
-        <v>-2.567118431456751</v>
+        <v>-2.3530683054493862</v>
       </c>
       <c r="C57">
         <v>214.35566444654796</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.1289625722274144</v>
+        <v>5.195908101983612</v>
       </c>
       <c r="B58">
-        <v>-2.3073967222905494</v>
+        <v>-2.0864891466227604</v>
       </c>
       <c r="C58">
         <v>214.35566444654796</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.2256274034310737</v>
+        <v>4.294429945516284</v>
       </c>
       <c r="B59">
-        <v>-2.0477852723864505</v>
+        <v>-1.8207483010907042</v>
       </c>
       <c r="C59">
         <v>214.35566444654796</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.3222273504725903</v>
+        <v>3.3926751652971108</v>
       </c>
       <c r="B60">
-        <v>-1.7883880426995662</v>
+        <v>-1.5559209810878318</v>
       </c>
       <c r="C60">
         <v>214.35566444654796</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.41874042772494</v>
+        <v>2.490627860435128</v>
       </c>
       <c r="B61">
-        <v>-1.5292776205245473</v>
+        <v>-1.2920596979033159</v>
       </c>
       <c r="C61">
         <v>214.35566444654796</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.5151446495611083</v>
+        <v>1.5882721300393865</v>
       </c>
       <c r="B62">
-        <v>-1.2705265931560483</v>
+        <v>-1.0292169628263319</v>
       </c>
       <c r="C62">
         <v>214.35566444654796</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.61147595695539</v>
+        <v>0.685633997969499</v>
       </c>
       <c r="B63">
-        <v>-1.0120162986114418</v>
+        <v>-0.76730683435703251</v>
       </c>
       <c r="C63">
         <v>214.35566444654796</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.29199800271263981</v>
+        <v>-0.21709281291262708</v>
       </c>
       <c r="B64">
-        <v>-0.75286307779898187</v>
+        <v>-0.50568955983948471</v>
       </c>
       <c r="C64">
         <v>214.35566444654796</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.1949516554620885</v>
+        <v>-1.1196726549945104</v>
       </c>
       <c r="B65">
-        <v>-0.491992022349643</v>
+        <v>-0.24358693382873423</v>
       </c>
       <c r="C65">
         <v>214.35566444654796</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.0970594273120655</v>
+        <v>-2.0218698806636732</v>
       </c>
       <c r="B66">
-        <v>-0.22832822389439811</v>
+        <v>0.019779249120173533</v>
       </c>
       <c r="C66">
         <v>214.35566444654796</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-2.9984163393755408</v>
+        <v>-2.9237532864150957</v>
       </c>
       <c r="B67">
-        <v>0.037814597811592493</v>
+        <v>0.28418179465364973</v>
       </c>
       <c r="C67">
         <v>214.35566444654796</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-3.9007997931409686</v>
+        <v>-3.8266094451736339</v>
       </c>
       <c r="B68">
-        <v>0.30056821051643662</v>
+        <v>0.54537190922394407</v>
       </c>
       <c r="C68">
         <v>214.35566444654796</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-4.8055864119432705</v>
+        <v>-4.7314348385972886</v>
       </c>
       <c r="B69">
-        <v>0.55538758288918477</v>
+        <v>0.80005880009233532</v>
       </c>
       <c r="C69">
         <v>214.35566444654796</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-5.7108673261277625</v>
+        <v>-5.636847806846748</v>
       </c>
       <c r="B70">
-        <v>0.80857499977939729</v>
+        <v>1.0528052769503857</v>
       </c>
       <c r="C70">
         <v>214.35566444654796</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-6.6145613326926034</v>
+        <v>-6.5413419534214157</v>
       </c>
       <c r="B71">
-        <v>1.0670017182764431</v>
+        <v>1.3085860813059138</v>
       </c>
       <c r="C71">
         <v>214.35566444654796</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-7.5171833882368766</v>
+        <v>-7.44529007667281</v>
       </c>
       <c r="B72">
-        <v>1.3289675682484052</v>
+        <v>1.5661700795014704</v>
       </c>
       <c r="C72">
         <v>214.35566444654796</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-8.4195938766905272</v>
+        <v>-8.3493150110322514</v>
       </c>
       <c r="B73">
-        <v>1.5916319237818211</v>
+        <v>1.8235004157910717</v>
       </c>
       <c r="C73">
         <v>214.35566444654796</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-9.32143873170601</v>
+        <v>-9.2531605403981452</v>
       </c>
       <c r="B74">
-        <v>1.8561637630583234</v>
+        <v>2.0814232212398651</v>
       </c>
       <c r="C74">
         <v>214.35566444654796</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-10.222053626727572</v>
+        <v>-10.156345876412047</v>
       </c>
       <c r="B75">
-        <v>2.1247564129911392</v>
+        <v>2.3415262569733253</v>
       </c>
       <c r="C75">
         <v>214.35566444654796</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-11.120747644644167</v>
+        <v>-11.058370992221065</v>
       </c>
       <c r="B76">
-        <v>2.3996909913247859</v>
+        <v>2.605460817547125</v>
       </c>
       <c r="C76">
         <v>214.35566444654796</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-12.016881039973624</v>
+        <v>-11.958772905076826</v>
       </c>
       <c r="B77">
-        <v>2.6830796686048095</v>
+        <v>2.8747558626307939</v>
       </c>
       <c r="C77">
         <v>214.35566444654796</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-12.910045344304539</v>
+        <v>-12.857256047143496</v>
       </c>
       <c r="B78">
-        <v>2.9762710357495741</v>
+        <v>3.1503874789190869</v>
       </c>
       <c r="C78">
         <v>214.35566444654796</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-13.799544644094565</v>
+        <v>-13.753316792406725</v>
       </c>
       <c r="B79">
-        <v>3.2815627066185753</v>
+        <v>3.4340188468807744</v>
       </c>
       <c r="C79">
         <v>214.35566444654796</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-14.684158453464193</v>
+        <v>-14.646071820191331</v>
       </c>
       <c r="B80">
-        <v>3.6029842123265841</v>
+        <v>3.7285670550950027</v>
       </c>
       <c r="C80">
         <v>214.35566444654796</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-15.560890442860361</v>
+        <v>-15.533352402000705</v>
       </c>
       <c r="B81">
-        <v>3.9504281729905393</v>
+        <v>4.0411941380373815</v>
       </c>
       <c r="C81">
         <v>214.35566444654796</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-16.375799724065303</v>
+        <v>-16.376114470239049</v>
       </c>
       <c r="B82">
-        <v>4.5019847173697531</v>
+        <v>4.500839683409664</v>
       </c>
       <c r="C82">
         <v>214.35566444654796</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-18.58215124481886</v>
+        <v>-18.586014949274933</v>
       </c>
       <c r="B1">
-        <v>4.3414201273000339</v>
+        <v>4.3248493514083943</v>
       </c>
       <c r="C1">
         <v>232.84072182980668</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-17.490152125014195</v>
+        <v>-17.513084686022317</v>
       </c>
       <c r="B2">
-        <v>4.3522118570074415</v>
+        <v>4.26081881667512</v>
       </c>
       <c r="C2">
         <v>232.84072182980668</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-16.434364535926175</v>
+        <v>-16.464390649419588</v>
       </c>
       <c r="B3">
-        <v>4.2195330702651672</v>
+        <v>4.1004019398805154</v>
       </c>
       <c r="C3">
         <v>232.84072182980668</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.384082755899975</v>
+        <v>-15.419534640206924</v>
       </c>
       <c r="B4">
-        <v>4.0650402023741634</v>
+        <v>3.9247214073113228</v>
       </c>
       <c r="C4">
         <v>232.84072182980668</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-14.337600793251552</v>
+        <v>-14.377383307251163</v>
       </c>
       <c r="B5">
-        <v>3.8954924127271457</v>
+        <v>3.7382845035202794</v>
       </c>
       <c r="C5">
         <v>232.84072182980668</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-13.294223558121118</v>
+        <v>-13.337474855096659</v>
       </c>
       <c r="B6">
-        <v>3.7136436556361843</v>
+        <v>3.5429277674782944</v>
       </c>
       <c r="C6">
         <v>232.84072182980668</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-12.253554593937388</v>
+        <v>-12.299545876672433</v>
       </c>
       <c r="B7">
-        <v>3.5210646967636388</v>
+        <v>3.3396987568110483</v>
       </c>
       <c r="C7">
         <v>232.84072182980668</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-11.215361082393315</v>
+        <v>-11.263441673127362</v>
       </c>
       <c r="B8">
-        <v>3.3186779650179434</v>
+        <v>3.1292127016282638</v>
       </c>
       <c r="C8">
         <v>232.84072182980668</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-10.179278581304216</v>
+        <v>-10.228920109684577</v>
       </c>
       <c r="B9">
-        <v>3.1079273846800413</v>
+        <v>2.9124325606349122</v>
       </c>
       <c r="C9">
         <v>232.84072182980668</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-9.144913533456215</v>
+        <v>-9.1957197117427754</v>
       </c>
       <c r="B10">
-        <v>2.8903722341237</v>
+        <v>2.6903982061149492</v>
       </c>
       <c r="C10">
         <v>232.84072182980668</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-8.1118875453962644</v>
+        <v>-8.1635890813287</v>
       </c>
       <c r="B11">
-        <v>2.6675117127214882</v>
+        <v>2.4641094360730236</v>
       </c>
       <c r="C11">
         <v>232.84072182980668</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-7.0799988499305773</v>
+        <v>-7.1323941568476217</v>
       </c>
       <c r="B12">
-        <v>2.4401452245008577</v>
+        <v>2.2340994072134723</v>
       </c>
       <c r="C12">
         <v>232.84072182980668</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-6.0497370211415884</v>
+        <v>-6.1024601455909639</v>
       </c>
       <c r="B13">
-        <v>2.2063330711099991</v>
+        <v>1.9990747853186981</v>
       </c>
       <c r="C13">
         <v>232.84072182980668</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-5.0213950159083289</v>
+        <v>-5.0739816414695289</v>
       </c>
       <c r="B14">
-        <v>1.9649145539012807</v>
+        <v>1.7582616794889208</v>
       </c>
       <c r="C14">
         <v>232.84072182980668</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.9937879810199663</v>
+        <v>-4.0461715159854812</v>
       </c>
       <c r="B15">
-        <v>1.7205840754230222</v>
+        <v>1.5147904630175626</v>
       </c>
       <c r="C15">
         <v>232.84072182980668</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.96582917470676</v>
+        <v>-3.0183078186023411</v>
       </c>
       <c r="B16">
-        <v>1.4776473195241657</v>
+        <v>1.2715322994882026</v>
       </c>
       <c r="C16">
         <v>232.84072182980668</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.9383021110531895</v>
+        <v>-1.9909110330376683</v>
       </c>
       <c r="B17">
-        <v>1.2329999940601679</v>
+        <v>1.0264172494518329</v>
       </c>
       <c r="C17">
         <v>232.84072182980668</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.91221845961607206</v>
+        <v>-0.96465321114254787</v>
       </c>
       <c r="B18">
-        <v>0.9826338521847543</v>
+        <v>0.77677259406744059</v>
       </c>
       <c r="C18">
         <v>232.84072182980668</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.11236774401259782</v>
+        <v>0.060429756951817591</v>
       </c>
       <c r="B19">
-        <v>0.726334804238207</v>
+        <v>0.52245559995858082</v>
       </c>
       <c r="C19">
         <v>232.84072182980668</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1.1356418727320492</v>
+        <v>1.0844610215442132</v>
       </c>
       <c r="B20">
-        <v>0.464837299857443</v>
+        <v>0.2639560301149475</v>
       </c>
       <c r="C20">
         <v>232.84072182980668</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2.1577892994414967</v>
+        <v>2.10756373293341</v>
       </c>
       <c r="B21">
-        <v>0.19887578867938302</v>
+        <v>0.0017636475262376022</v>
       </c>
       <c r="C21">
         <v>232.84072182980668</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>3.1789624088086494</v>
+        <v>3.129839125329382</v>
       </c>
       <c r="B22">
-        <v>-0.070945979425658293</v>
+        <v>-0.26371894408003238</v>
       </c>
       <c r="C22">
         <v>232.84072182980668</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>4.1991816325751188</v>
+        <v>4.1513007685868475</v>
       </c>
       <c r="B23">
-        <v>-0.34454705365377375</v>
+        <v>-0.53243777802505288</v>
       </c>
       <c r="C23">
         <v>232.84072182980668</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>5.2184344142510133</v>
+        <v>5.1719403164717246</v>
       </c>
       <c r="B24">
-        <v>-0.621977182967662</v>
+        <v>-0.80442604689219532</v>
       </c>
       <c r="C24">
         <v>232.84072182980668</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>6.2367081973464265</v>
+        <v>6.1917494227499237</v>
       </c>
       <c r="B25">
-        <v>-0.90328611633001932</v>
+        <v>-1.0797169432648281</v>
       </c>
       <c r="C25">
         <v>232.84072182980668</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>7.2539850025689141</v>
+        <v>7.2107161371849724</v>
       </c>
       <c r="B26">
-        <v>-1.1885450879118544</v>
+        <v>-1.3583579926755443</v>
       </c>
       <c r="C26">
         <v>232.84072182980668</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8.2702251594158938</v>
+        <v>8.2288140935309073</v>
       </c>
       <c r="B27">
-        <v>-1.4779112727174408</v>
+        <v>-1.6404540524538434</v>
       </c>
       <c r="C27">
         <v>232.84072182980668</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9.28538357458223</v>
+        <v>9.2460133215393725</v>
       </c>
       <c r="B28">
-        <v>-1.7715633309593588</v>
+        <v>-1.9261243128784436</v>
       </c>
       <c r="C28">
         <v>232.84072182980668</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>10.299415154762786</v>
+        <v>10.262283850962001</v>
       </c>
       <c r="B29">
-        <v>-2.06967992285019</v>
+        <v>-2.2154879642280658</v>
       </c>
       <c r="C29">
         <v>232.84072182980668</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>11.3122994109488</v>
+        <v>11.277612054879276</v>
       </c>
       <c r="B30">
-        <v>-2.3723422260869449</v>
+        <v>-2.5085992001255932</v>
       </c>
       <c r="C30">
         <v>232.84072182980668</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>12.32411427131699</v>
+        <v>12.292049679686951</v>
       </c>
       <c r="B31">
-        <v>-2.6792414883043256</v>
+        <v>-2.8052522275705556</v>
       </c>
       <c r="C31">
         <v>232.84072182980668</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.334962268340446</v>
+        <v>13.305664815109614</v>
       </c>
       <c r="B32">
-        <v>-2.9899714746214636</v>
+        <v>-3.1051762569066437</v>
       </c>
       <c r="C32">
         <v>232.84072182980668</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>14.344945934492253</v>
+        <v>14.318525550871849</v>
       </c>
       <c r="B33">
-        <v>-3.30412595015749</v>
+        <v>-3.4081004984775505</v>
       </c>
       <c r="C33">
         <v>232.84072182980668</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>15.354128087489903</v>
+        <v>15.330673592110678</v>
       </c>
       <c r="B34">
-        <v>-3.6214560303667764</v>
+        <v>-3.7138590929001274</v>
       </c>
       <c r="C34">
         <v>232.84072182980668</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>16.362412686028421</v>
+        <v>16.342045105612822</v>
       </c>
       <c r="B35">
-        <v>-3.9423422320446577</v>
+        <v>-4.0227059018838585</v>
       </c>
       <c r="C35">
         <v>232.84072182980668</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>17.369663974047249</v>
+        <v>17.352549873577452</v>
       </c>
       <c r="B36">
-        <v>-4.2673224223217163</v>
+        <v>-4.3349997174113906</v>
       </c>
       <c r="C36">
         <v>232.84072182980668</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>18.375746195485824</v>
+        <v>18.362097678203725</v>
       </c>
       <c r="B37">
-        <v>-4.5969344683285325</v>
+        <v>-4.65109933146537</v>
       </c>
       <c r="C37">
         <v>232.84072182980668</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>19.380426171392571</v>
+        <v>19.370533581120434</v>
       </c>
       <c r="B38">
-        <v>-4.9321022278514421</v>
+        <v>-4.9716209267157359</v>
       </c>
       <c r="C38">
         <v>232.84072182980668</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>20.383081031251869</v>
+        <v>20.377443761674847</v>
       </c>
       <c r="B39">
-        <v>-5.275293521299802</v>
+        <v>-5.29821024858158</v>
       </c>
       <c r="C39">
         <v>232.84072182980668</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>21.382990481657096</v>
+        <v>21.38234967864387</v>
       </c>
       <c r="B40">
-        <v>-5.6293621597387311</v>
+        <v>-5.6327704331692932</v>
       </c>
       <c r="C40">
         <v>232.84072182980668</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>22.379434229201628</v>
+        <v>22.3847727908044</v>
       </c>
       <c r="B41">
-        <v>-5.9971619542333432</v>
+        <v>-5.9772046165852615</v>
       </c>
       <c r="C41">
         <v>232.84072182980668</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>22.379434229201628</v>
+        <v>22.3847727908044</v>
       </c>
       <c r="B42">
-        <v>-5.9971619542333432</v>
+        <v>-5.9772046165852615</v>
       </c>
       <c r="C42">
         <v>232.84072182980668</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>21.348959403947489</v>
+        <v>21.359742452211947</v>
       </c>
       <c r="B43">
-        <v>-5.76419369537697</v>
+        <v>-5.7226783174040126</v>
       </c>
       <c r="C43">
         <v>232.84072182980668</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>20.320863444285205</v>
+        <v>20.336111921155258</v>
       </c>
       <c r="B44">
-        <v>-5.5218003426824573</v>
+        <v>-5.4625850489947778</v>
       </c>
       <c r="C44">
         <v>232.84072182980668</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>19.294426311135577</v>
+        <v>19.313402909840086</v>
       </c>
       <c r="B45">
-        <v>-5.2728346995665811</v>
+        <v>-5.19882693958923</v>
       </c>
       <c r="C45">
         <v>232.84072182980668</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>18.268927965419419</v>
+        <v>18.29113713047218</v>
       </c>
       <c r="B46">
-        <v>-5.0201495694461125</v>
+        <v>-4.9333061174190362</v>
       </c>
       <c r="C46">
         <v>232.84072182980668</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>17.243745782207434</v>
+        <v>17.268901007117449</v>
       </c>
       <c r="B47">
-        <v>-4.7662117997145366</v>
+        <v>-4.6676673546688292</v>
       </c>
       <c r="C47">
         <v>232.84072182980668</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>16.218646793169814</v>
+        <v>16.246539811282272</v>
       </c>
       <c r="B48">
-        <v>-4.5119444136721771</v>
+        <v>-4.4025259993350581</v>
       </c>
       <c r="C48">
         <v>232.84072182980668</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>15.193495444126658</v>
+        <v>15.223963526333188</v>
       </c>
       <c r="B49">
-        <v>-4.2578844785960683</v>
+        <v>-4.1382400433671318</v>
       </c>
       <c r="C49">
         <v>232.84072182980668</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>14.168156180898034</v>
+        <v>14.201082135636721</v>
       </c>
       <c r="B50">
-        <v>-4.00456906176324</v>
+        <v>-3.8751674787144545</v>
       </c>
       <c r="C50">
         <v>232.84072182980668</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>13.142533154243818</v>
+        <v>13.177831997365834</v>
       </c>
       <c r="B51">
-        <v>-3.752377919005951</v>
+        <v>-3.6135614059524785</v>
       </c>
       <c r="C51">
         <v>232.84072182980668</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>12.116689334682951</v>
+        <v>12.154254968919123</v>
       </c>
       <c r="B52">
-        <v>-3.5010615603773312</v>
+        <v>-3.3532553601608064</v>
       </c>
       <c r="C52">
         <v>232.84072182980668</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>11.090727397674153</v>
+        <v>11.130419282501611</v>
       </c>
       <c r="B53">
-        <v>-3.2502131844857334</v>
+        <v>-3.0939779850450808</v>
       </c>
       <c r="C53">
         <v>232.84072182980668</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>10.06475001867614</v>
+        <v>10.106393170318322</v>
       </c>
       <c r="B54">
-        <v>-2.9994259899395073</v>
+        <v>-2.8354579243109459</v>
       </c>
       <c r="C54">
         <v>232.84072182980668</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>9.03883525933112</v>
+        <v>9.0822285117589487</v>
       </c>
       <c r="B55">
-        <v>-2.7483906955815112</v>
+        <v>-2.5774888560472862</v>
       </c>
       <c r="C55">
         <v>232.84072182980668</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>8.0129627260152354</v>
+        <v>8.05791177495185</v>
       </c>
       <c r="B56">
-        <v>-2.4971881011926134</v>
+        <v>-2.3201245958759449</v>
       </c>
       <c r="C56">
         <v>232.84072182980668</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>6.9870874112881172</v>
+        <v>7.0334130752100572</v>
       </c>
       <c r="B57">
-        <v>-2.2459965267881885</v>
+        <v>-2.0634839938020066</v>
       </c>
       <c r="C57">
         <v>232.84072182980668</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5.9611643077093985</v>
+        <v>6.0087025278466122</v>
       </c>
       <c r="B58">
-        <v>-1.9949942923836128</v>
+        <v>-1.8076858998305574</v>
       </c>
       <c r="C58">
         <v>232.84072182980668</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>4.9351538211646027</v>
+        <v>4.9837538427337575</v>
       </c>
       <c r="B59">
-        <v>-1.7443382703324768</v>
+        <v>-1.5528348685724238</v>
       </c>
       <c r="C59">
         <v>232.84072182980668</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3.9090380108428908</v>
+        <v>3.9585551079806667</v>
       </c>
       <c r="B60">
-        <v>-1.4940995423412584</v>
+        <v>-1.2989782730614148</v>
       </c>
       <c r="C60">
         <v>232.84072182980668</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2.882804349259326</v>
+        <v>2.9330980062557379</v>
       </c>
       <c r="B61">
-        <v>-1.2443277424546564</v>
+        <v>-1.0461491909370844</v>
       </c>
       <c r="C61">
         <v>232.84072182980668</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>1.8564403089289618</v>
+        <v>1.9073742202273576</v>
       </c>
       <c r="B62">
-        <v>-0.99507250471736586</v>
+        <v>-0.79438069983898374</v>
       </c>
       <c r="C62">
         <v>232.84072182980668</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>0.82996634074280373</v>
+        <v>0.88139733883197546</v>
       </c>
       <c r="B63">
-        <v>-0.74625280245541692</v>
+        <v>-0.54361875720119546</v>
       </c>
       <c r="C63">
         <v>232.84072182980668</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.19646519090440351</v>
+        <v>-0.14473142392176797</v>
       </c>
       <c r="B64">
-        <v>-0.4972649661201588</v>
+        <v>-0.29346083963591191</v>
       </c>
       <c r="C64">
         <v>232.84072182980668</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.2226689432419626</v>
+        <v>-1.1708889477571702</v>
       </c>
       <c r="B65">
-        <v>-0.24737466544427528</v>
+        <v>-0.043417303549857691</v>
       </c>
       <c r="C65">
         <v>232.84072182980668</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2484595734991908</v>
+        <v>-2.1969521123975411</v>
       </c>
       <c r="B66">
-        <v>0.0041524298395533791</v>
+        <v>0.20700149465024628</v>
       </c>
       <c r="C66">
         <v>232.84072182980668</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-3.2738911553124876</v>
+        <v>-3.2229568458840734</v>
       </c>
       <c r="B67">
-        <v>0.25710207933915824</v>
+        <v>0.45765267082164163</v>
       </c>
       <c r="C67">
         <v>232.84072182980668</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-4.2999754279466584</v>
+        <v>-4.2495752695295472</v>
       </c>
       <c r="B68">
-        <v>0.50746576002443156</v>
+        <v>0.70586322987743644</v>
       </c>
       <c r="C68">
         <v>232.84072182980668</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-5.327495986607433</v>
+        <v>-5.2773279478861559</v>
       </c>
       <c r="B69">
-        <v>0.75213885834745386</v>
+        <v>0.94956291089304035</v>
       </c>
       <c r="C69">
         <v>232.84072182980668</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-6.3553661846358773</v>
+        <v>-6.3054930251921828</v>
       </c>
       <c r="B70">
-        <v>0.9954266813270054</v>
+        <v>1.1916225005372143</v>
       </c>
       <c r="C70">
         <v>232.84072182980668</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-7.3824012725492958</v>
+        <v>-7.3332834763114381</v>
       </c>
       <c r="B71">
-        <v>1.2420232205393313</v>
+        <v>1.4351719610389782</v>
       </c>
       <c r="C71">
         <v>232.84072182980668</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-8.4088943314345546</v>
+        <v>-8.3608940189237142</v>
       </c>
       <c r="B72">
-        <v>1.4907672852238276</v>
+        <v>1.6794369092750241</v>
       </c>
       <c r="C72">
         <v>232.84072182980668</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-9.4353350694074773</v>
+        <v>-9.38864999388025</v>
       </c>
       <c r="B73">
-        <v>1.7397186459868308</v>
+        <v>1.923123479866597</v>
       </c>
       <c r="C73">
         <v>232.84072182980668</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-10.461521872130076</v>
+        <v>-10.41641749190206</v>
       </c>
       <c r="B74">
-        <v>1.9896761012392819</v>
+        <v>2.1667642237654685</v>
       </c>
       <c r="C74">
         <v>232.84072182980668</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-11.487076508485158</v>
+        <v>-11.443945276778162</v>
       </c>
       <c r="B75">
-        <v>2.2421382071771703</v>
+        <v>2.4113582956552171</v>
       </c>
       <c r="C75">
         <v>232.84072182980668</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-12.511605602692461</v>
+        <v>-12.470972054699848</v>
       </c>
       <c r="B76">
-        <v>2.4986635233320875</v>
+        <v>2.6579448488161281</v>
       </c>
       <c r="C76">
         <v>232.84072182980668</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-13.534744903730514</v>
+        <v>-13.497255881378033</v>
       </c>
       <c r="B77">
-        <v>2.7606952165941046</v>
+        <v>2.9074860843921475</v>
       </c>
       <c r="C77">
         <v>232.84072182980668</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-14.556261804275984</v>
+        <v>-14.522642268199872</v>
       </c>
       <c r="B78">
-        <v>3.0291548799516126</v>
+        <v>3.1605963963851611</v>
       </c>
       <c r="C78">
         <v>232.84072182980668</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-15.575760067691604</v>
+        <v>-15.546868027251326</v>
       </c>
       <c r="B79">
-        <v>3.3056124076858238</v>
+        <v>3.4183224708439415</v>
       </c>
       <c r="C79">
         <v>232.84072182980668</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-16.592544841773634</v>
+        <v>-16.569471599893127</v>
       </c>
       <c r="B80">
-        <v>3.5928208125126537</v>
+        <v>3.6824999049317064</v>
       </c>
       <c r="C80">
         <v>232.84072182980668</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-17.604910386119215</v>
+        <v>-17.589319885385471</v>
       </c>
       <c r="B81">
-        <v>3.8975382582458145</v>
+        <v>3.9576349873985333</v>
       </c>
       <c r="C81">
         <v>232.84072182980668</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-18.58215124481886</v>
+        <v>-18.586014949274933</v>
       </c>
       <c r="B82">
-        <v>4.3414201273000339</v>
+        <v>4.3248493514083943</v>
       </c>
       <c r="C82">
         <v>232.84072182980668</v>
